--- a/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 28,09,26 днрсч ост зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино КИ и ЗПФ/расчеты Останкино ЗПФ/дв 28,09,26 днрсч ост зпф.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6232217-1E9B-4ACF-A50F-2961076C582F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55F112AC-DFA7-44F6-89E2-B45A65483E66}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="52">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -181,6 +178,12 @@
   </si>
   <si>
     <t>7216 СОЧНЫЕ СО СЛ.МАСЛ.ПМ пельм пл.0.7кг зам. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>05,10,</t>
   </si>
 </sst>
 </file>
@@ -752,49 +755,49 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AE3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="AF3" s="1"/>
       <c r="AG3" s="1"/>
@@ -830,43 +833,45 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q4" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AC4" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
@@ -931,7 +936,7 @@
       </c>
       <c r="Q5" s="4">
         <f t="shared" si="0"/>
-        <v>329.43399999999997</v>
+        <v>350</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
@@ -978,7 +983,7 @@
       <c r="AD5" s="1"/>
       <c r="AE5" s="4">
         <f>SUM(AE6:AE500)</f>
-        <v>135.45399999999998</v>
+        <v>146.4</v>
       </c>
       <c r="AF5" s="1"/>
       <c r="AG5" s="1"/>
@@ -1000,10 +1005,10 @@
     </row>
     <row r="6" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
@@ -1022,7 +1027,7 @@
         <v>120</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -1038,12 +1043,11 @@
         <v>1.2</v>
       </c>
       <c r="Q6" s="5">
-        <f>15*P6-O6-F6</f>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R6" s="1">
         <f>(F6+O6+Q6)/P6</f>
-        <v>15</v>
+        <v>18.333333333333336</v>
       </c>
       <c r="S6" s="1">
         <f>(F6+O6)/P6</f>
@@ -1080,11 +1084,11 @@
         <v>0.6</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AE6" s="1">
-        <f>G6*Q6</f>
-        <v>6.72</v>
+        <f t="shared" ref="AE6:AE16" si="3">G6*Q6</f>
+        <v>8.4</v>
       </c>
       <c r="AF6" s="1"/>
       <c r="AG6" s="1"/>
@@ -1106,10 +1110,10 @@
     </row>
     <row r="7" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="C7" s="1">
         <v>27.428000000000001</v>
@@ -1128,7 +1132,7 @@
         <v>120</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1">
@@ -1142,16 +1146,15 @@
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1">
-        <f t="shared" ref="P7:P16" si="3">E7/5</f>
+        <f t="shared" ref="P7:P16" si="4">E7/5</f>
         <v>2.7412000000000001</v>
       </c>
       <c r="Q7" s="5">
-        <f t="shared" ref="Q7:Q16" si="4">15*P7-O7-F7</f>
-        <v>27.396000000000001</v>
+        <v>30</v>
       </c>
       <c r="R7" s="1">
         <f t="shared" ref="R7:R16" si="5">(F7+O7+Q7)/P7</f>
-        <v>15</v>
+        <v>15.949948927477017</v>
       </c>
       <c r="S7" s="1">
         <f t="shared" ref="S7:S16" si="6">(F7+O7)/P7</f>
@@ -1189,8 +1192,8 @@
       </c>
       <c r="AD7" s="1"/>
       <c r="AE7" s="1">
-        <f>G7*Q7</f>
-        <v>27.396000000000001</v>
+        <f t="shared" si="3"/>
+        <v>30</v>
       </c>
       <c r="AF7" s="1"/>
       <c r="AG7" s="1"/>
@@ -1212,10 +1215,10 @@
     </row>
     <row r="8" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
@@ -1234,7 +1237,7 @@
         <v>120</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J8" s="1"/>
       <c r="K8" s="1">
@@ -1248,16 +1251,15 @@
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.90800000000000003</v>
       </c>
       <c r="Q8" s="5">
-        <f t="shared" si="4"/>
-        <v>9.0380000000000003</v>
+        <v>10</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>16.059471365638768</v>
       </c>
       <c r="S8" s="1">
         <f t="shared" si="6"/>
@@ -1294,11 +1296,11 @@
         <v>0</v>
       </c>
       <c r="AD8" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AE8" s="1">
-        <f>G8*Q8</f>
-        <v>9.0380000000000003</v>
+        <f t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1"/>
@@ -1320,10 +1322,10 @@
     </row>
     <row r="9" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -1340,7 +1342,7 @@
         <v>120</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1">
@@ -1356,7 +1358,7 @@
         <v>30</v>
       </c>
       <c r="P9" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.2</v>
       </c>
       <c r="Q9" s="5"/>
@@ -1399,10 +1401,10 @@
         <v>1.8</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AE9" s="1">
-        <f>G9*Q9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF9" s="1"/>
@@ -1425,10 +1427,10 @@
     </row>
     <row r="10" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1">
         <v>16</v>
@@ -1449,7 +1451,7 @@
         <v>120</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1465,7 +1467,7 @@
         <v>170</v>
       </c>
       <c r="P10" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="Q10" s="5"/>
@@ -1509,7 +1511,7 @@
       </c>
       <c r="AD10" s="1"/>
       <c r="AE10" s="1">
-        <f>G10*Q10</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF10" s="1"/>
@@ -1532,10 +1534,10 @@
     </row>
     <row r="11" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1">
         <v>73</v>
@@ -1552,7 +1554,7 @@
         <v>120</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1568,7 +1570,7 @@
         <v>250</v>
       </c>
       <c r="P11" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>14.6</v>
       </c>
       <c r="Q11" s="5"/>
@@ -1612,7 +1614,7 @@
       </c>
       <c r="AD11" s="1"/>
       <c r="AE11" s="1">
-        <f>G11*Q11</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AF11" s="1"/>
@@ -1635,10 +1637,10 @@
     </row>
     <row r="12" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
         <v>40</v>
@@ -1659,7 +1661,7 @@
         <v>120</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1675,11 +1677,10 @@
         <v>10</v>
       </c>
       <c r="P12" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="Q12" s="5">
-        <f t="shared" si="4"/>
         <v>80</v>
       </c>
       <c r="R12" s="1">
@@ -1722,7 +1723,7 @@
       </c>
       <c r="AD12" s="1"/>
       <c r="AE12" s="1">
-        <f>G12*Q12</f>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="AF12" s="1"/>
@@ -1745,10 +1746,10 @@
     </row>
     <row r="13" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1">
         <v>113</v>
@@ -1767,7 +1768,7 @@
         <v>120</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1783,16 +1784,15 @@
         <v>10</v>
       </c>
       <c r="P13" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>11.8</v>
       </c>
       <c r="Q13" s="5">
-        <f t="shared" si="4"/>
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="R13" s="1">
         <f t="shared" si="5"/>
-        <v>14.999999999999998</v>
+        <v>15.423728813559322</v>
       </c>
       <c r="S13" s="1">
         <f t="shared" si="6"/>
@@ -1830,8 +1830,8 @@
       </c>
       <c r="AD13" s="1"/>
       <c r="AE13" s="1">
-        <f>G13*Q13</f>
-        <v>34.5</v>
+        <f t="shared" si="3"/>
+        <v>36</v>
       </c>
       <c r="AF13" s="1"/>
       <c r="AG13" s="1"/>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="14" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
@@ -1877,7 +1877,7 @@
         <v>120</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1891,16 +1891,15 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>11.4</v>
       </c>
       <c r="Q14" s="5">
-        <f t="shared" si="4"/>
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>15.350877192982455</v>
       </c>
       <c r="S14" s="1">
         <f t="shared" si="6"/>
@@ -1938,8 +1937,8 @@
       </c>
       <c r="AD14" s="1"/>
       <c r="AE14" s="1">
-        <f>G14*Q14</f>
-        <v>19.599999999999998</v>
+        <f t="shared" si="3"/>
+        <v>21</v>
       </c>
       <c r="AF14" s="1"/>
       <c r="AG14" s="1"/>
@@ -1961,10 +1960,10 @@
     </row>
     <row r="15" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -1977,7 +1976,7 @@
         <v>120</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
@@ -1993,7 +1992,7 @@
         <v>30</v>
       </c>
       <c r="P15" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="Q15" s="5">
@@ -2038,10 +2037,10 @@
         <v>3.6</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AE15" s="1">
-        <f>G15*Q15</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="AF15" s="1"/>
@@ -2064,10 +2063,10 @@
     </row>
     <row r="16" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1">
         <v>128</v>
@@ -2086,7 +2085,7 @@
         <v>180</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1">
@@ -2100,16 +2099,15 @@
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6.6</v>
       </c>
       <c r="Q16" s="5">
-        <f t="shared" si="4"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R16" s="1">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>15.606060606060607</v>
       </c>
       <c r="S16" s="1">
         <f t="shared" si="6"/>
@@ -2147,8 +2145,8 @@
       </c>
       <c r="AD16" s="1"/>
       <c r="AE16" s="1">
-        <f>G16*Q16</f>
-        <v>4.1999999999999993</v>
+        <f t="shared" si="3"/>
+        <v>7</v>
       </c>
       <c r="AF16" s="1"/>
       <c r="AG16" s="1"/>
